--- a/excel/reference-prices.xlsx
+++ b/excel/reference-prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sambit\fusiontest\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{922C965F-A854-4C0C-AFE5-13DB0AE8F7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90AC640F-F10D-415E-8219-BBAB38535816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="11170" xr2:uid="{5F68713D-8659-4224-B9D7-A24403B60FE5}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{4423A5AB-B279-4029-8537-8101108CFC38}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Prices" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
   <si>
     <t>Category</t>
   </si>
@@ -71,7 +71,13 @@
     <t>Ea</t>
   </si>
   <si>
-    <t>EXAMPLE — replace with real rate</t>
+    <t>DERIVED — lowest of 4 price(s) paid for this item in the 90-day window as of 2026-08-21. NOT an authoritative negotiated contract rate — replace with a real rate when available.</t>
+  </si>
+  <si>
+    <t>Recruiting expenses</t>
+  </si>
+  <si>
+    <t>DERIVED — lowest of 3 price(s) paid for this item in the 90-day window as of 2026-08-21. NOT an authoritative negotiated contract rate — replace with a real rate when available.</t>
   </si>
   <si>
     <t>Contractor Expense</t>
@@ -80,10 +86,52 @@
     <t>Outside Contractors</t>
   </si>
   <si>
+    <t>DERIVED — lowest of 24 price(s) paid for this item in the 90-day window as of 2026-08-21. NOT an authoritative negotiated contract rate — replace with a real rate when available.</t>
+  </si>
+  <si>
     <t>Marketing General</t>
   </si>
   <si>
     <t>Marketing Expenses</t>
+  </si>
+  <si>
+    <t>Miscellaneous</t>
+  </si>
+  <si>
+    <t>Therapy - Supplies</t>
+  </si>
+  <si>
+    <t>Cafeteria Subsidies</t>
+  </si>
+  <si>
+    <t>DERIVED — lowest of 5 price(s) paid for this item in the 90-day window as of 2026-08-21. NOT an authoritative negotiated contract rate — replace with a real rate when available.</t>
+  </si>
+  <si>
+    <t>962.58 Professional Services</t>
+  </si>
+  <si>
+    <t>Killowatts of Green Energy</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Activities - Entertainment</t>
+  </si>
+  <si>
+    <t>Purchase</t>
+  </si>
+  <si>
+    <t>Housekeeping Supplies</t>
+  </si>
+  <si>
+    <t>Advertising Consulting</t>
+  </si>
+  <si>
+    <t>Hr</t>
   </si>
 </sst>
 </file>
@@ -463,16 +511,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD510E6D-1FE7-4C8B-9670-68210DE07060}">
-  <dimension ref="A1:G4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B456AE3-5398-487C-8B28-841D09A83F6C}">
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="144.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
@@ -506,7 +555,7 @@
         <v>7</v>
       </c>
       <c r="D2">
-        <v>1450000</v>
+        <v>1407010</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -523,10 +572,10 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>15000</v>
+        <v>84680</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -535,7 +584,7 @@
         <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -546,7 +595,7 @@
         <v>14</v>
       </c>
       <c r="D4">
-        <v>12000</v>
+        <v>14204</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -555,6 +604,146 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>11321</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>7744</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>61401</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9">
+        <v>4347</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10">
+        <v>5848</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
         <v>10</v>
       </c>
     </row>

--- a/excel/reference-prices.xlsx
+++ b/excel/reference-prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sambit\fusiontest\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90AC640F-F10D-415E-8219-BBAB38535816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1832260C-2502-473F-94EF-AA5785D52123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{4423A5AB-B279-4029-8537-8101108CFC38}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" xr2:uid="{4423A5AB-B279-4029-8537-8101108CFC38}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Prices" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Category</t>
   </si>
@@ -60,78 +60,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>Business Liability Insurance</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>Ea</t>
-  </si>
-  <si>
-    <t>DERIVED — lowest of 4 price(s) paid for this item in the 90-day window as of 2026-08-21. NOT an authoritative negotiated contract rate — replace with a real rate when available.</t>
-  </si>
-  <si>
-    <t>Recruiting expenses</t>
-  </si>
-  <si>
-    <t>DERIVED — lowest of 3 price(s) paid for this item in the 90-day window as of 2026-08-21. NOT an authoritative negotiated contract rate — replace with a real rate when available.</t>
-  </si>
-  <si>
-    <t>Contractor Expense</t>
-  </si>
-  <si>
-    <t>Outside Contractors</t>
-  </si>
-  <si>
-    <t>DERIVED — lowest of 24 price(s) paid for this item in the 90-day window as of 2026-08-21. NOT an authoritative negotiated contract rate — replace with a real rate when available.</t>
-  </si>
-  <si>
-    <t>Marketing General</t>
-  </si>
-  <si>
-    <t>Marketing Expenses</t>
-  </si>
-  <si>
-    <t>Miscellaneous</t>
-  </si>
-  <si>
-    <t>Therapy - Supplies</t>
-  </si>
-  <si>
-    <t>Cafeteria Subsidies</t>
-  </si>
-  <si>
-    <t>DERIVED — lowest of 5 price(s) paid for this item in the 90-day window as of 2026-08-21. NOT an authoritative negotiated contract rate — replace with a real rate when available.</t>
-  </si>
-  <si>
-    <t>962.58 Professional Services</t>
-  </si>
-  <si>
-    <t>Killowatts of Green Energy</t>
-  </si>
-  <si>
-    <t>kWh</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Activities - Entertainment</t>
-  </si>
-  <si>
-    <t>Purchase</t>
-  </si>
-  <si>
-    <t>Housekeeping Supplies</t>
-  </si>
-  <si>
-    <t>Advertising Consulting</t>
-  </si>
-  <si>
-    <t>Hr</t>
   </si>
 </sst>
 </file>
@@ -512,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B456AE3-5398-487C-8B28-841D09A83F6C}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
@@ -547,206 +475,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>1407010</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>84680</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4">
-        <v>14204</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5">
-        <v>11321</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6">
-        <v>7744</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>61401</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9">
-        <v>4347</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10">
-        <v>5848</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>42</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/reference-prices.xlsx
+++ b/excel/reference-prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sambit\fusiontest\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1832260C-2502-473F-94EF-AA5785D52123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C480703F-4E98-41E3-A1EC-0BC59030DD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="19200" windowHeight="11170" xr2:uid="{4423A5AB-B279-4029-8537-8101108CFC38}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{4423A5AB-B279-4029-8537-8101108CFC38}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Prices" sheetId="1" r:id="rId1"/>
